--- a/section-a/programs/datamodel.xlsx
+++ b/section-a/programs/datamodel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kaushalya\consultancy\nhce\2026\nhce\mba\powerbi\workshop\section-a\programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE757B6F-31C1-4B40-B6AE-774017B5D21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3AFCC0-C98A-4709-92BA-84AB5075E8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="1" r:id="rId1"/>
@@ -471,7 +471,8 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
